--- a/docs/StructureDefinition-LTCPractitionerRole.xlsx
+++ b/docs/StructureDefinition-LTCPractitionerRole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T05:34:23+08:00</t>
+    <t>2026-02-28T07:16:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCPractitionerRole.xlsx
+++ b/docs/StructureDefinition-LTCPractitionerRole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T07:16:04+08:00</t>
+    <t>2026-02-28T23:13:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCPractitionerRole.xlsx
+++ b/docs/StructureDefinition-LTCPractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T23:13:53+08:00</t>
+    <t>2026-03-01T19:25:35+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCPractitionerRole.xlsx
+++ b/docs/StructureDefinition-LTCPractitionerRole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:25:35+08:00</t>
+    <t>2026-03-02T02:26:08+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCPractitionerRole.xlsx
+++ b/docs/StructureDefinition-LTCPractitionerRole.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3238" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3237" uniqueCount="452">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T02:26:08+08:00</t>
+    <t>2026-04-02T13:32:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -749,14 +749,10 @@
     <t>https://twcore.mohw.gov.tw/ig/twcore/ValueSet/health-professional-sct-tw</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE</t>
-  </si>
-  <si>
-    <t>CD</t>
+    <t>PRD-1 / STF-18  / PRA-3  / PRT-4  / ROL-3 / ORC-12 / OBR-16 / PV1-7 / PV1-8 / PV1-9 / PV1-17</t>
+  </si>
+  <si>
+    <t>.code</t>
   </si>
   <si>
     <t>PractitionerRole.specialty</t>
@@ -765,10 +761,16 @@
     <t>健康照護服務提供者的特定專業</t>
   </si>
   <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
+  </si>
+  <si>
+    <t>PRA-5</t>
+  </si>
+  <si>
+    <t>.player.HealthCareProvider[@classCode = 'PROV'].code</t>
+  </si>
+  <si>
+    <t>./Specialty</t>
   </si>
   <si>
     <t>PractitionerRole.specialty.id</t>
@@ -812,10 +814,10 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
-    <t>CV</t>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
   </si>
   <si>
     <t>PractitionerRole.specialty.coding:TWMedicalDepartmentSCT</t>
@@ -1116,7 +1118,7 @@
     <t>PractitionerRole.healthcareService</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(HealthcareService)
+    <t xml:space="preserve">Reference(HealthcareService|4.0.1)
 </t>
   </si>
   <si>
@@ -1403,7 +1405,7 @@
     <t>PractitionerRole.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -1765,7 +1767,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="48.5546875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="73.27734375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="67.37109375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="166.7265625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
@@ -4876,7 +4878,7 @@
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
         <v>227</v>
@@ -4949,19 +4951,19 @@
         <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>234</v>
+        <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="AL28" t="s" s="2">
-        <v>236</v>
-      </c>
       <c r="AM28" t="s" s="2">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>20</v>
@@ -4969,10 +4971,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4992,20 +4994,18 @@
         <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
         <v>227</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>239</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5036,7 +5036,7 @@
         <v>232</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>20</v>
@@ -5054,7 +5054,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -5063,19 +5063,19 @@
         <v>78</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>234</v>
+        <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>20</v>
+        <v>241</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>20</v>
@@ -5083,10 +5083,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5112,10 +5112,10 @@
         <v>178</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5195,10 +5195,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5224,10 +5224,10 @@
         <v>134</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5307,10 +5307,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5330,22 +5330,22 @@
         <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5382,7 +5382,7 @@
         <v>20</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AC32" s="2"/>
       <c r="AD32" t="s" s="2">
@@ -5392,7 +5392,7 @@
         <v>187</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5401,16 +5401,16 @@
         <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>234</v>
+        <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>20</v>
@@ -5421,13 +5421,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>20</v>
@@ -5446,22 +5446,22 @@
         <v>20</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5486,11 +5486,11 @@
         <v>20</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>20</v>
@@ -5508,7 +5508,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5517,16 +5517,16 @@
         <v>78</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>234</v>
+        <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>20</v>
@@ -5537,10 +5537,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5566,10 +5566,10 @@
         <v>178</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5649,10 +5649,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5678,13 +5678,13 @@
         <v>134</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5763,10 +5763,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5792,16 +5792,16 @@
         <v>101</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -5811,7 +5811,7 @@
         <v>20</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>20</v>
@@ -5850,7 +5850,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5865,10 +5865,10 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>20</v>
@@ -5879,10 +5879,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5908,13 +5908,13 @@
         <v>178</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5964,7 +5964,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5979,10 +5979,10 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>20</v>
@@ -5993,10 +5993,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6022,14 +6022,14 @@
         <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6078,7 +6078,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -6093,10 +6093,10 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>20</v>
@@ -6107,10 +6107,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6136,14 +6136,14 @@
         <v>178</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6192,7 +6192,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6207,10 +6207,10 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>20</v>
@@ -6221,10 +6221,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6250,16 +6250,16 @@
         <v>155</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -6308,7 +6308,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6323,10 +6323,10 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>20</v>
@@ -6337,13 +6337,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>20</v>
@@ -6362,22 +6362,22 @@
         <v>20</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6402,11 +6402,11 @@
         <v>20</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>20</v>
@@ -6424,7 +6424,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6433,16 +6433,16 @@
         <v>78</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>234</v>
+        <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>20</v>
@@ -6453,10 +6453,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6482,10 +6482,10 @@
         <v>178</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6565,10 +6565,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6594,13 +6594,13 @@
         <v>134</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6679,10 +6679,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6708,16 +6708,16 @@
         <v>101</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -6727,7 +6727,7 @@
         <v>20</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>20</v>
@@ -6766,7 +6766,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6781,10 +6781,10 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>20</v>
@@ -6795,10 +6795,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6824,13 +6824,13 @@
         <v>178</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6880,7 +6880,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6895,10 +6895,10 @@
         <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>20</v>
@@ -6909,10 +6909,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6938,14 +6938,14 @@
         <v>107</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -6994,7 +6994,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -7009,10 +7009,10 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>20</v>
@@ -7023,10 +7023,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7052,14 +7052,14 @@
         <v>178</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7108,7 +7108,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -7123,10 +7123,10 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>20</v>
@@ -7137,10 +7137,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7166,16 +7166,16 @@
         <v>155</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -7224,7 +7224,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7239,10 +7239,10 @@
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>20</v>
@@ -7253,13 +7253,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>20</v>
@@ -7278,22 +7278,22 @@
         <v>20</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7318,11 +7318,11 @@
         <v>20</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>20</v>
@@ -7340,7 +7340,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7349,16 +7349,16 @@
         <v>78</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>234</v>
+        <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>20</v>
@@ -7369,10 +7369,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7398,10 +7398,10 @@
         <v>178</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7481,10 +7481,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7510,13 +7510,13 @@
         <v>134</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7595,10 +7595,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7624,16 +7624,16 @@
         <v>101</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -7643,7 +7643,7 @@
         <v>20</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>20</v>
@@ -7682,7 +7682,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7697,10 +7697,10 @@
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>20</v>
@@ -7711,10 +7711,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7740,13 +7740,13 @@
         <v>178</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7796,7 +7796,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7811,10 +7811,10 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>20</v>
@@ -7825,10 +7825,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7854,14 +7854,14 @@
         <v>107</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -7910,7 +7910,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7925,10 +7925,10 @@
         <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>20</v>
@@ -7939,10 +7939,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7968,14 +7968,14 @@
         <v>178</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -8024,7 +8024,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -8039,10 +8039,10 @@
         <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>20</v>
@@ -8053,10 +8053,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8082,16 +8082,16 @@
         <v>155</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -8140,7 +8140,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -8155,10 +8155,10 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>20</v>
@@ -8169,10 +8169,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8198,16 +8198,16 @@
         <v>178</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -8256,7 +8256,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -8271,10 +8271,10 @@
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>20</v>
@@ -8285,10 +8285,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8311,13 +8311,13 @@
         <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8368,7 +8368,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8386,21 +8386,21 @@
         <v>20</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8509,10 +8509,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8623,10 +8623,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8652,7 +8652,7 @@
         <v>178</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M61" t="s" s="2">
         <v>191</v>
@@ -8737,10 +8737,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8851,10 +8851,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8965,10 +8965,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9079,10 +9079,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9105,13 +9105,13 @@
         <v>20</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9162,7 +9162,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -9177,10 +9177,10 @@
         <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>20</v>
@@ -9191,10 +9191,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9217,17 +9217,17 @@
         <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -9276,7 +9276,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -9294,7 +9294,7 @@
         <v>20</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>20</v>
@@ -9305,10 +9305,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9417,10 +9417,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9531,10 +9531,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9560,10 +9560,10 @@
         <v>107</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9590,13 +9590,13 @@
         <v>20</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>20</v>
@@ -9614,7 +9614,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -9623,19 +9623,19 @@
         <v>87</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>20</v>
@@ -9643,10 +9643,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9672,16 +9672,16 @@
         <v>178</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -9730,7 +9730,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -9745,13 +9745,13 @@
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>20</v>
@@ -9759,10 +9759,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9788,16 +9788,16 @@
         <v>107</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>20</v>
@@ -9822,13 +9822,13 @@
         <v>20</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>20</v>
@@ -9846,7 +9846,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -9861,13 +9861,13 @@
         <v>99</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>20</v>
@@ -9875,10 +9875,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9901,16 +9901,16 @@
         <v>88</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9960,7 +9960,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -9989,10 +9989,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10018,10 +10018,10 @@
         <v>164</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10072,7 +10072,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -10090,10 +10090,10 @@
         <v>131</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>20</v>
@@ -10101,10 +10101,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10127,16 +10127,16 @@
         <v>20</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10186,7 +10186,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
@@ -10204,7 +10204,7 @@
         <v>20</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>20</v>
@@ -10215,10 +10215,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10327,10 +10327,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10441,14 +10441,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -10470,10 +10470,10 @@
         <v>134</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>137</v>
@@ -10528,7 +10528,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>77</v>
@@ -10557,10 +10557,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10586,10 +10586,10 @@
         <v>107</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10616,13 +10616,13 @@
         <v>20</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>20</v>
@@ -10640,7 +10640,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>77</v>
@@ -10658,7 +10658,7 @@
         <v>20</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>20</v>
@@ -10669,10 +10669,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10698,10 +10698,10 @@
         <v>155</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -10752,7 +10752,7 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>77</v>
@@ -10770,7 +10770,7 @@
         <v>20</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>20</v>
@@ -10781,10 +10781,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10807,16 +10807,16 @@
         <v>20</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -10866,7 +10866,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>77</v>
@@ -10884,7 +10884,7 @@
         <v>20</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>20</v>
@@ -10895,10 +10895,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10921,16 +10921,16 @@
         <v>20</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -10980,7 +10980,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>77</v>
@@ -10998,7 +10998,7 @@
         <v>20</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>20</v>
@@ -11009,10 +11009,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11035,13 +11035,13 @@
         <v>20</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11092,7 +11092,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>77</v>
@@ -11110,7 +11110,7 @@
         <v>20</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>20</v>
@@ -11121,10 +11121,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11233,10 +11233,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11347,14 +11347,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -11376,10 +11376,10 @@
         <v>134</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>137</v>
@@ -11434,7 +11434,7 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>77</v>
@@ -11463,10 +11463,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11492,10 +11492,10 @@
         <v>178</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -11546,7 +11546,7 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>87</v>
@@ -11575,10 +11575,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11604,10 +11604,10 @@
         <v>164</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11658,7 +11658,7 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>77</v>
@@ -11676,7 +11676,7 @@
         <v>20</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>20</v>
@@ -11687,10 +11687,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11716,10 +11716,10 @@
         <v>178</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11770,7 +11770,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>77</v>
@@ -11788,7 +11788,7 @@
         <v>20</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>20</v>
@@ -11799,10 +11799,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11825,17 +11825,17 @@
         <v>20</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>20</v>
@@ -11884,7 +11884,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>77</v>

--- a/docs/StructureDefinition-LTCPractitionerRole.xlsx
+++ b/docs/StructureDefinition-LTCPractitionerRole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T13:32:15+08:00</t>
+    <t>2026-04-03T21:17:06+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCPractitionerRole.xlsx
+++ b/docs/StructureDefinition-LTCPractitionerRole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T21:17:06+08:00</t>
+    <t>2026-06-25T08:48:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
